--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_38_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_38_R4.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8311</v>
+        <v>5.5012</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5639</v>
+        <v>4.1668</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2672</v>
+        <v>1.3344</v>
       </c>
       <c r="G2" t="n">
         <v>3.3095</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5938</v>
+        <v>1.2639</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9006</v>
+        <v>0.5034</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6932</v>
+        <v>0.7604</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4654</v>
+        <v>4.951</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5903</v>
+        <v>5.3111</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1248</v>
+        <v>-0.3601</v>
       </c>
       <c r="G3" t="n">
         <v>2.5637</v>
@@ -688,13 +688,13 @@
         <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8991</v>
+        <v>1.3847</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6018</v>
+        <v>0.3227</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2973</v>
+        <v>1.062</v>
       </c>
       <c r="V3" t="n">
         <v>1.4665</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.258</v>
+        <v>2.3822</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3634</v>
+        <v>3.6557</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1054</v>
+        <v>-1.2735</v>
       </c>
       <c r="G4" t="n">
         <v>1.9061</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2797</v>
+        <v>0.4039</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9006</v>
+        <v>0.1928</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3791</v>
+        <v>0.2111</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9029</v>
+        <v>1.6169</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9656</v>
+        <v>5.8476</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.0627</v>
+        <v>-4.2307</v>
       </c>
       <c r="G5" t="n">
         <v>0.4066</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3519</v>
+        <v>0.0659</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U5" t="n">
-        <v>0.163</v>
+        <v>-0.005</v>
       </c>
       <c r="V5" t="n">
         <v>1.6083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4953</v>
+        <v>0.9398</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7186</v>
+        <v>0.3647</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2155</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8705</v>
+        <v>1.315</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1993</v>
+        <v>0.8454</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6713</v>
+        <v>0.4696</v>
       </c>
       <c r="V6" t="n">
         <v>1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1602</v>
+        <v>0.3617</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1274</v>
+        <v>0.2264</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0328</v>
+        <v>0.1353</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6614</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4266</v>
+        <v>0.0953</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>0.1298</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.314</v>
+        <v>-0.1543</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3783</v>
+        <v>0.0502</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0643</v>
+        <v>-0.2046</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9276</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0053</v>
+        <v>0.165</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8962</v>
+        <v>-0.4676</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9015</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2693</v>
+        <v>-1.3117</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4612</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8081</v>
+        <v>-1.3216</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4209</v>
+        <v>-0.1888</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1633</v>
+        <v>1.8187</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2576</v>
+        <v>-2.0076</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1466</v>
+        <v>-0.0139</v>
       </c>
       <c r="K9" t="n">
-        <v>0.521</v>
+        <v>1.4116</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6257</v>
+        <v>-1.4255</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7257</v>
+        <v>-0.175</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3577</v>
+        <v>0.4071</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.368</v>
+        <v>-0.5821</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7117</v>
+        <v>0.0237</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0307</v>
+        <v>0.4617</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2836</v>
+        <v>-1.6083</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2836</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9479</v>
+        <v>-1.3688</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-2.0928</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1844</v>
+        <v>0.7241</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3724</v>
+        <v>-0.3447</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2353</v>
+        <v>0.9268</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1372</v>
+        <v>-1.2715</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1744</v>
+        <v>-1.1062</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1008</v>
+        <v>0.3193</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0736</v>
+        <v>-1.4255</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.7615</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3361</v>
+        <v>0.6075</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2108</v>
+        <v>0.154</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.127</v>
+        <v>0.744</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1494</v>
+        <v>0.1731</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0224</v>
+        <v>0.5709</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3558</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1942</v>
+        <v>-1.6784</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5366</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6576</v>
+        <v>-1.1508</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1888</v>
+        <v>-0.3724</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8187</v>
+        <v>-0.2353</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0076</v>
+        <v>-0.1372</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0139</v>
+        <v>0.1744</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4116</v>
+        <v>0.1008</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4255</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.175</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4071</v>
+        <v>-0.3361</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5821</v>
+        <v>-0.2108</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3971</v>
+        <v>0.1426</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5228</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1256</v>
+        <v>0.056</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6083</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3521</v>
+        <v>-1.8755</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6393</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2872</v>
+        <v>-0.9425</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3447</v>
+        <v>0.4209</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9268</v>
+        <v>0.1633</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2715</v>
+        <v>0.2576</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1062</v>
+        <v>1.1466</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3193</v>
+        <v>0.521</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4255</v>
+        <v>0.6257</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7615</v>
+        <v>-0.7257</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6075</v>
+        <v>-0.3577</v>
       </c>
       <c r="O12" t="n">
-        <v>0.154</v>
+        <v>-0.368</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2394</v>
+        <v>0.0747</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3734</v>
+        <v>0.2399</v>
       </c>
       <c r="U12" t="n">
-        <v>0.134</v>
+        <v>-0.1652</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5329</v>
+        <v>-6.8087</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9806</v>
+        <v>-6.3909</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5523</v>
+        <v>-0.4178</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9627</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7714</v>
+        <v>-0.0472</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8215</v>
+        <v>-0.2317</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0501</v>
+        <v>0.1845</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.182099999999998</v>
+        <v>2.555399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.314800000000002</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.132700000000001</v>
+        <v>-7.1327</v>
       </c>
       <c r="G14" t="n">
-        <v>3.933700000000002</v>
+        <v>3.933700000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>9.7056</v>
+        <v>9.705599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.7721</v>
+        <v>-5.772099999999998</v>
       </c>
       <c r="J14" t="n">
         <v>15.7103</v>
@@ -1537,22 +1537,22 @@
         <v>-8.4475</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.118399999999999</v>
+        <v>-8.118400000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2368</v>
       </c>
       <c r="R14" t="n">
-        <v>8.118599999999999</v>
+        <v>8.118600000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7197</v>
+        <v>6.0932</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5156</v>
+        <v>1.8889</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2043</v>
+        <v>4.2041</v>
       </c>
       <c r="V14" t="n">
         <v>0.6468</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0928</v>
+        <v>3.6386</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0277</v>
+        <v>3.2083</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.4303</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7664</v>
+        <v>1.8243</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2784</v>
+        <v>0.9544</v>
       </c>
       <c r="I15" t="n">
-        <v>0.512</v>
+        <v>0.8699</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8384</v>
+        <v>3.3221</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3627</v>
+        <v>2.1846</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2011</v>
+        <v>1.1374</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6048</v>
+        <v>-1.4978</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9157</v>
+        <v>-1.2303</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6891</v>
+        <v>-0.2676</v>
       </c>
       <c r="P15" t="n">
         <v>2.0876</v>
@@ -1624,28 +1624,28 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6273</v>
+        <v>-0.2732</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0272</v>
+        <v>-0.1138</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6546</v>
+        <v>-0.1595</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0761</v>
+        <v>3.5716</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4442</v>
+        <v>3.9098</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6319</v>
+        <v>-0.3382</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8243</v>
+        <v>-0.7664</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9544</v>
+        <v>-1.2784</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8699</v>
+        <v>0.512</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3221</v>
+        <v>0.8384</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1846</v>
+        <v>-0.3627</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1374</v>
+        <v>1.2011</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4978</v>
+        <v>-1.6048</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2303</v>
+        <v>-0.9157</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2676</v>
+        <v>-0.6891</v>
       </c>
       <c r="P16" t="n">
         <v>2.0876</v>
@@ -1702,22 +1702,22 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1643</v>
+        <v>0.1061</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1221</v>
+        <v>-0.1452</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0422</v>
+        <v>0.2513</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9034</v>
+        <v>3.3073</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8951</v>
+        <v>4.131</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9917</v>
+        <v>-0.8236</v>
       </c>
       <c r="G17" t="n">
         <v>1.9274</v>
@@ -1780,13 +1780,13 @@
         <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.256</v>
+        <v>-0.852</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0297</v>
+        <v>-0.7938</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2262</v>
+        <v>-0.0582</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.791</v>
+        <v>0.8246</v>
       </c>
       <c r="E18" t="n">
         <v>0.6304</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1606</v>
+        <v>0.1942</v>
       </c>
       <c r="G18" t="n">
         <v>0.3794</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2842</v>
+        <v>-0.2506</v>
       </c>
       <c r="T18" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0424</v>
+        <v>-0.9752</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0043</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0382</v>
+        <v>-0.971</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8552999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1871</v>
+        <v>-0.1199</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MUURINEN</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6607</v>
+        <v>-1.2799</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7906</v>
+        <v>-0.7227</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8701</v>
+        <v>-0.5572</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4736</v>
+        <v>-1.1508</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3025</v>
+        <v>-0.7359</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1711</v>
+        <v>-0.4149</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7159</v>
+        <v>1.2623</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0336</v>
+        <v>1.6707</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.4084</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7577</v>
+        <v>-2.4131</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3361</v>
+        <v>-2.4066</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4216</v>
+        <v>-0.0065</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1871</v>
+        <v>-0.9847</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0747</v>
+        <v>-0.8252</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1125</v>
+        <v>-0.1595</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>M. MUURINEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8354</v>
+        <v>-1.5935</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0765</v>
+        <v>-0.7906</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7589</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1508</v>
+        <v>-1.4736</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7359</v>
+        <v>-0.3025</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4149</v>
+        <v>-1.1711</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2623</v>
+        <v>-0.7159</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6707</v>
+        <v>0.0336</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4084</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4131</v>
+        <v>-0.7577</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.4066</v>
+        <v>-0.3361</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0065</v>
+        <v>-0.4216</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5515</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5402</v>
+        <v>-0.1199</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1791</v>
+        <v>-0.0747</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3611</v>
+        <v>-0.0452</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9349</v>
+        <v>-3.0529</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4618</v>
+        <v>-2.5797</v>
       </c>
       <c r="F23" t="n">
         <v>-0.4732</v>
@@ -2248,10 +2248,10 @@
         <v>3.0154</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6054</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5421</v>
+        <v>-0.6601</v>
       </c>
       <c r="U23" t="n">
         <v>-0.0633</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4506</v>
+        <v>-3.5696</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.01</v>
+        <v>-1.0476</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4406</v>
+        <v>-2.522</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5202</v>
+        <v>-2.6558</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2832</v>
+        <v>-2.2376</v>
       </c>
       <c r="I24" t="n">
-        <v>0.763</v>
+        <v>-0.4182</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7668</v>
+        <v>-0.2538</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1043</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6625</v>
+        <v>0.4282</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.287</v>
+        <v>-2.402</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3875</v>
+        <v>-1.5556</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1005</v>
+        <v>-0.8464</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5671</v>
+        <v>-1.2333</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.094</v>
+        <v>-0.7938</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4731</v>
+        <v>-0.4395</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4355</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3633</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>-1.0722</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8391</v>
+        <v>-3.7709</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2835</v>
+        <v>-2.3639</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5556</v>
+        <v>-1.407</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6558</v>
+        <v>-0.5202</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.2376</v>
+        <v>-1.2832</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4182</v>
+        <v>0.763</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2538</v>
+        <v>0.7668</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.1043</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4282</v>
+        <v>0.6625</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.402</v>
+        <v>-1.287</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.5556</v>
+        <v>-1.3875</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8464</v>
+        <v>0.1005</v>
       </c>
       <c r="P25" t="n">
-        <v>1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R25" t="n">
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5028</v>
+        <v>-0.8874</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0297</v>
+        <v>-0.4479</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4731</v>
+        <v>-0.4395</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0722</v>
+        <v>-1.4355</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.3633</v>
       </c>
       <c r="X25" t="n">
         <v>-1.0722</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.1818</v>
+        <v>-2.181899999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>6.596599999999999</v>
+        <v>6.5966</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.778600000000001</v>
+        <v>-8.778499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-3.9336</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.705499999999999</v>
+        <v>-9.705500000000001</v>
       </c>
       <c r="I26" t="n">
         <v>5.7719</v>
@@ -2458,7 +2458,7 @@
         <v>11.7769</v>
       </c>
       <c r="K26" t="n">
-        <v>3.329200000000001</v>
+        <v>3.3292</v>
       </c>
       <c r="L26" t="n">
         <v>8.4475</v>
@@ -2482,10 +2482,10 @@
         <v>16.2368</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.7196</v>
+        <v>-5.7195</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.2041</v>
+        <v>-4.2042</v>
       </c>
       <c r="U26" t="n">
         <v>-1.5155</v>
